--- a/02_referencias.xlsx
+++ b/02_referencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ulisesgtgm\Documents\Github\Repositories\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE04EA65-BD81-4B14-B332-9F308B762602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B07CBE5B-4B73-4BE0-8584-205D41EE438D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1C41D898-66DE-4C07-9513-BA7DBB54818A}"/>
   </bookViews>
@@ -36,9 +36,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="2">
   <si>
     <t>sumatoria</t>
+  </si>
+  <si>
+    <t>fijo</t>
   </si>
 </sst>
 </file>
@@ -410,7 +413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18A6DBED-BBE3-4F8D-885D-24FCFD93F385}">
-  <dimension ref="B2:E2"/>
+  <dimension ref="B2:E7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
@@ -428,6 +431,44 @@
         <v>10</v>
       </c>
     </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <f>C5+C$4</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C6">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <f t="shared" ref="D6:D7" si="0">C6+C$4</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C7">
+        <v>30</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
